--- a/LLM_Extraction_and_CrossCritique/interactive-table/gt-vs-runs_pipeline1.xlsx
+++ b/LLM_Extraction_and_CrossCritique/interactive-table/gt-vs-runs_pipeline1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="379">
   <si>
     <t>Query</t>
   </si>
@@ -2071,6 +2071,875 @@
     <t>{
   "selected_filter": {
     "ICI Class": "PD-1",
+    "Cancer Type": "Non-Small Cell Lung Cancer"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma",
+    "Type of Therapy": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Clinical setting in relation to surgery",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Type of combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Study name"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "CTLA-4",
+    "Cancer Type": "Gastric/GEJ"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Total sample size",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Cancer type"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3",
+    "Type of Therapy": "Monotherapy",
+    "Cancer Type": "Urothelial"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Follow-up duration for primary endpoint(s) in months",
+    "Column 6": "Name of ICI",
+    "Column 7": "Primary endpoint",
+    "Column 8": "Total sample size",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Clinical Setting": "Adjuvant"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Control regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Renal Cell Carcinoma (RCC)",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Type of combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Type of control"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-L1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Cancer type",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Type of combination",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Total sample size",
+    "Column 7": "Cancer type",
+    "Column 8": "Name of ICI",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Study name",
+    "Column 8": "Name of ICI",
+    "Column 9": "Control regimen",
+    "Column 10": "Cancer type"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-1",
+    "Type of Therapy": "Monotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-L1",
+    "Type of Therapy": "Combination Therapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Type of combination",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "CTLA-4",
+    "Type of Therapy": "Monotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Cancer type",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "CTLA-4",
+    "Type of Therapy": "Combination Therapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Type of combination",
+    "Column 8": "Cancer type",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3",
+    "ICI Name": "Pembrolizumab",
+    "Cancer Type": "Non-Small Cell Lung Cancer"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Trial phase",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Nivolumab",
+    "Cancer Type": "Melanoma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Monotherapy/combination",
+    "Column 7": "Type of combination",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Atezolizumab",
+    "Cancer Type": "Breast",
+    "Type of combination (Treatment Arm)": "ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Cancer type",
+    "Column 7": "Type of combination",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Is PD-L1 positivity inclusion criteria",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Avelumab",
+    "Cancer Type": "Urothelial"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Cancer type",
+    "Column 7": "Clinical setting in relation to surgery",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Tremelimumab",
+    "Cancer Type": "Hepatocellular carcinoma (HCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Type of combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Durvalumab",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of Therapy": "Monotherapy",
+    "Clinical Setting": "Maintenance",
+    "Trial Phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3",
+    "ICI Class": "PD-1",
+    "Cancer Type": "Non-Small Cell Lung Cancer",
+    "Type of Therapy": "Combination Therapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Total sample size",
+    "Column 7": "Name of ICI",
+    "Column 8": "Type of combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-L1",
+    "Type of Therapy": "Monotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Study name",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of Therapy": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Type of combination",
+    "Column 10": "Study name"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of Therapy": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Name of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Total sample size",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of Therapy": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + TKI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Type of combination",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + RadiatICln (Radiation/Clinical Radiation)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Type of combination",
+    "Column 6": "Name of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + Vaccine"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Type of combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma",
+    "Type of combination (Treatment Arm)": "ICI + BRAFi + MEKi"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Type of combination",
+    "Column 8": "Cancer type",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + Anti-VEGF"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Type of combination",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Cancer type",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of Therapy": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + Chemo + Anti-VEGF"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Name of ICI",
+    "Column 9": "Class of ICI",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3",
+    "Control Arm": "Placebo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Control regimen",
+    "Column 9": "Type of control",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Control Arm": "Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Control regimen",
+    "Column 9": "Type of control",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Hepatocellular carcinoma (HCC)",
+    "Control Arm": "TKI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Control regimen",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Trial phase",
+    "Column 10": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Interferon"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Trial phase",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Study name"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Best Supportive Care (BSC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Control regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Chemo / Anti-EGFR"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Control regimen",
+    "Column 7": "Cancer type",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Trial phase",
+    "Column 10": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Chemo / Anti-VEGF"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Control regimen",
+    "Column 9": "Type of combination",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "mTOR inhibitor",
+    "Cancer Type": "Renal Cell Carcinoma (RCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Name of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Trial phase",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Multikinase inhibitor"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Vaccine"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Name of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Trial phase",
+    "Column 10": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Radiation"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Type of control",
+    "Column 7": "Cancer type",
+    "Column 8": "Clinical setting in relation to surgery",
+    "Column 9": "Trial phase",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma",
+    "Clinical Setting": "Adjuvant"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Control regimen",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Clinical Setting": "Neoadjuvant",
     "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
   },
   "selected_column": {
@@ -2078,7 +2947,2186 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "Path CR (Pathologic Complete Response; pCR)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Clinical setting in relation to surgery",
+    "Column 7": "Cancer type",
+    "Column 8": "Name of ICI",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "ORR"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Study name",
+    "Column 7": "Name of ICI",
+    "Column 8": "Cancer type",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Study name",
+    "Column 7": "Cancer type",
+    "Column 8": "Name of ICI",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "PFS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Study name",
+    "Column 7": "Cancer type",
+    "Column 8": "Name of ICI",
+    "Column 9": "Control regimen",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "RFS (Recurrence-/Relapse-Free Survival)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Clinical setting in relation to surgery",
+    "Column 9": "Control regimen",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "EFS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Study name",
+    "Column 7": "Cancer type",
+    "Column 8": "Name of ICI",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "Safety"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Secondary endpoint",
+    "Column 7": "Name of ICI",
+    "Column 8": "Cancer type",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Is PD-L1 positivity inclusion criteria": "Yes"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Is PD-L1 positivity inclusion criteria"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Colorectal"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Is any other biomarker used for inclusion",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Pancreatic Cancer"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Is any other biomarker used for inclusion",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Prostate"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Monotherapy/combination",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Is PD-L1 positivity inclusion criteria",
+    "Column 9": "Is any other biomarker used for inclusion",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Multiple Myeloma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Trial phase",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Mesothelioma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Type of combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer",
+    "Type of Study": "Follow-up"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Control regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma",
+    "Type of Study": "Follow-up"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Original/Follow Up",
+    "Column 7": "Name of ICI",
+    "Column 8": "Type of combination",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Primary multiple, composite, or co-primary endpoints?",
+    "Column 7": "Study name",
+    "Column 8": "Cancer type",
+    "Column 9": "Name of ICI",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Follow-up duration for primary endpoint(s) in months",
+    "Column 7": "Study name",
+    "Column 8": "Cancer type",
+    "Column 9": "Name of ICI",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "PFS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Follow-up duration for primary endpoint(s) in months",
+    "Column 7": "Study name",
+    "Column 8": "Cancer type",
+    "Column 9": "Name of ICI",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Number of arms",
+    "Column 6": "Study name",
+    "Column 7": "Cancer type",
+    "Column 8": "Name of ICI",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Lines of treatment",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Bladder",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Lines of treatment"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "ICI Name": "Pembrolizumab",
+    "Type of Therapy": "Monotherapy",
+    "Control Arm": "Chemo",
+    "Trial Phase": "Phase 3",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)",
+    "ICI Class": "PD-1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Control regimen",
+    "Column 8": "Cancer type",
+    "Column 9": "Trial phase",
+    "Column 10": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Type of combination",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Secondary endpoint",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of Study": "Follow-up"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Original/Follow Up",
+    "Column 6": "Primary endpoint",
+    "Column 7": "Secondary endpoint",
+    "Column 8": "Type of follow-up given",
+    "Column 9": "Follow-up duration for primary endpoint(s) in months",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Included in MA": "Yes"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Included in MA"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Included in MA": "No"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Trial phase",
+    "Column 10": "Included in MA"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Renal Cell Carcinoma (RCC)",
+    "Type of Study": "Original publication"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Control regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3",
+    "Cancer Type": "Gastric/GEJ",
+    "ICI Class": "PD-L1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-1",
+    "Cancer Type": "Esophageal/GEJ"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Small Cell Lung Cancer (SCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Type of combination",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)",
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Breast"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Trial phase",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Gastric/GEJ"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Lines of treatment"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Hepatocellular carcinoma (HCC)",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Lines of treatment",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Renal Cell Carcinoma (RCC)",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Monotherapy/combination",
+    "Column 7": "Type of combination",
+    "Column 8": "Control regimen",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Lines of treatment"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Clinical Setting": "Perioperative"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Clinical setting in relation to surgery",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Monotherapy/combination",
+    "Column 7": "Control regimen",
+    "Column 8": "Lines of treatment",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Name of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Study name",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + MEKi"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Type of combination",
+    "Column 7": "Cancer type",
+    "Column 8": "Study name",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Type of combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Monotherapy/combination",
+    "Column 6": "Name of ICI",
+    "Column 7": "Type of combination",
+    "Column 8": "Control regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)",
+    "Type of Therapy": "Combination Therapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Type of combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Is PD-L1 positivity inclusion criteria": "No"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Type of combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Is PD-L1 positivity inclusion criteria"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Renal Cell Carcinoma (RCC)",
+    "Type of Therapy": "Combination Therapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Type of combination",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Cancer type",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Small Cell Lung Cancer (SCLC)",
+    "Type of Therapy": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Trial phase",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of Therapy": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Type of combination",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of Therapy": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Type of combination",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Lines of treatment",
+    "Column 6": "Name of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Clinical setting in relation to surgery",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Follow-up duration for primary endpoint(s) in months",
+    "Column 6": "Study name",
+    "Column 7": "Cancer type",
+    "Column 8": "Name of ICI",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Pembrolizumab",
+    "Cancer Type": "Melanoma",
+    "Clinical Setting": "Adjuvant"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Clinical setting in relation to surgery",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Total sample size",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma",
+    "Type of Therapy": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Clinical setting in relation to surgery",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Type of combination",
+    "Column 9": "Study name",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3",
+    "Type of Therapy": "Monotherapy",
+    "Cancer Type": "Urothelial"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Follow-up duration for primary endpoint(s) in months",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Clinical Setting": "Adjuvant"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Type of Therapy",
+    "Column 8": "Control regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-L1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Cancer type",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Type of combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
     "Column 5": "Treatment regimen",
+    "Column 6": "Primary endpoint",
+    "Column 7": "Study name",
+    "Column 8": "Name of ICI",
+    "Column 9": "Control regimen",
+    "Column 10": "Cancer type"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-1",
+    "Type of Therapy": "Monotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Study name"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "CTLA-4",
+    "Type of Therapy": "Monotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Clinical setting in relation to surgery",
+    "Column 8": "Trial phase",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "CTLA-4",
+    "Type of Therapy": "Combination Therapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Type of combination",
+    "Column 8": "Cancer type",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3",
+    "ICI Name": "Pembrolizumab",
+    "Cancer Type": "NSCLC"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Control regimen",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Avelumab",
+    "Cancer Type": "Bladder"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Cancer type",
+    "Column 7": "Clinical setting in relation to surgery",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-L1",
+    "Type of Therapy": "Monotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Cancer type",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Type of combination",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma",
+    "Type of Therapy": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + BRAFi + MEKi"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + Anti-VEGF"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Type of combination",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Cancer type",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of Therapy": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + Chemo + Anti-VEGF"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Name of ICI",
+    "Column 8": "Type of combination",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Cancer type",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3",
+    "Control Arm": "Placebo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Control Arm": "Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Chemo / Anti-EGFR"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Control regimen",
+    "Column 7": "Cancer type",
+    "Column 8": "Type of combination",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Chemo / Anti-VEGF"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Name of ICI",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "mTOR inhibitor",
+    "Cancer Type": "Renal Cell Carcinoma (RCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Name of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Trial phase",
+    "Column 10": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Radiation"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Type of control",
+    "Column 7": "Cancer type",
+    "Column 8": "Trial phase",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Study name"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Clinical Setting": "Neoadjuvant"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Clinical setting in relation to surgery",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "PFS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Study name",
+    "Column 7": "Cancer type",
+    "Column 8": "Name of ICI",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "RFS (Recurrence-/Relapse-Free Survival)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Study name",
+    "Column 7": "Cancer type",
+    "Column 8": "Name of ICI",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "EFS (Event-Free Survival) (in combos like Path CR+EFS)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Study name",
+    "Column 7": "Cancer type",
+    "Column 8": "Name of ICI",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Is PD-L1 positivity inclusion criteria",
+    "Column 6": "Study name",
+    "Column 7": "Name of ICI",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Colorectal"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Is any other biomarker used for inclusion",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Prostate"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Control regimen",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Is any other biomarker used for inclusion",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Multiple Myeloma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Lines of treatment",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Bladder",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Lines of treatment",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Study name",
+    "Column 7": "Name of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Renal Cell Carcinoma (RCC)",
+    "Type of Study": "Original publication"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Gastric/GEJ",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Clinical setting in relation to surgery",
+    "Column 8": "Lines of treatment",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Monotherapy/combination",
+    "Column 6": "Type of combination",
+    "Column 7": "Name of ICI",
+    "Column 8": "Control regimen",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Control regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Is PD-L1 positivity inclusion criteria"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Study name"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Renal Cell Carcinoma (RCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Type of combination",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Small Cell Lung Cancer (SCLC)",
+    "Type of Therapy": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Type of combination",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Cancer type"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Lines of treatment",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Follow-up duration for primary endpoint(s) in months",
+    "Column 6": "Study name",
+    "Column 7": "Cancer type",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Name of ICI"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Pembrolizumab",
+    "Cancer Type": "Melanoma",
+    "Clinical Setting": "Adjuvant"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Clinical setting in relation to surgery",
+    "Column 7": "Cancer type",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Study name",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "CTLA-4",
+    "Cancer Type": "Gastric/GEJ"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Total sample size",
+    "Column 7": "Name of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-L1",
+    "Type of Therapy": "Combination Therapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Cancer type",
+    "Column 7": "Type of combination",
+    "Column 8": "Clinical setting in relation to surgery",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Name of ICI",
+    "Column 7": "Study name",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Atezolizumab",
+    "Cancer Type": "Breast",
+    "Type of combination (Treatment Arm)": "ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Type of combination",
+    "Column 10": "Is PD-L1 positivity inclusion criteria"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of Therapy": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Name of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of Therapy": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + TKI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Type of combination",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Hepatocellular carcinoma (HCC)",
+    "Control Arm": "TKI (Tyrosine Kinase Inhibitor)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Control regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Cancer type"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Best Supportive Care (BSC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "Path CR",
+    "Clinical Setting": "Neoadjuvant"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Clinical setting in relation to surgery",
+    "Column 7": "Cancer type",
+    "Column 8": "Name of ICI",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Study name",
+    "Column 7": "Cancer type",
+    "Column 8": "Name of ICI",
+    "Column 9": "Control regimen",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "Safety"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Study name",
+    "Column 7": "Cancer type",
+    "Column 8": "Name of ICI",
+    "Column 9": "Control regimen",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Pancreatic Cancer"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Is PD-L1 positivity inclusion criteria",
+    "Column 9": "Is any other biomarker used for inclusion",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Mesothelioma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
     "Column 6": "Name of ICI",
     "Column 7": "Class of ICI",
     "Column 8": "Monotherapy/combination",
@@ -2091,7 +5139,7 @@
     <t>{
   "selected_filter": {
     "Cancer Type": "Melanoma",
-    "Type of Therapy": "Combination Therapy"
+    "Type of Study": "Follow-up"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -2099,38 +5147,39 @@
     "Column 3": "Authors",
     "Column 4": "Year",
     "Column 5": "Study name",
-    "Column 6": "Clinical setting in relation to surgery",
-    "Column 7": "Treatment regimen",
-    "Column 8": "Name of ICI",
-    "Column 9": "Type of combination",
-    "Column 10": "Control regimen"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Gastric/GEJ",
-    "ICI Class": "CTLA-4"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Total sample size",
-    "Column 7": "Name of ICI",
-    "Column 8": "Control regimen",
-    "Column 9": "Monotherapy/combination",
-    "Column 10": "Lines of treatment"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Bladder",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "PFS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Follow-up duration for primary endpoint(s) in months",
+    "Column 7": "Study name",
+    "Column 8": "Cancer type",
+    "Column 9": "Name of ICI",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "ICI Name": "Pembrolizumab",
+    "Control Arm": "Chemo",
     "Trial Phase": "Phase 3",
     "Type of Therapy": "Monotherapy"
   },
@@ -2139,113 +5188,37 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Primary Endpoint",
-    "Column 7": "Control regimen",
-    "Column 8": "Follow-up duration for primary endpoint(s) in months [Overall]",
-    "Column 9": "Follow-up duration for primary endpoint(s) in months [Rx]",
-    "Column 10": "Follow-up duration for primary endpoint(s) in months [Control]"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Clinical Setting in relation to surgery": "Adjuvant"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Total sample size",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "CTLA-4",
-    "Cancer Type": "Renal Cell Carcinoma (RCC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Class of ICI",
-    "Column 7": "Treatment regimen",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "PD-L1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Monotherapy/combination",
-    "Column 8": "Type of combination",
-    "Column 9": "Control regimen",
-    "Column 10": "Primary endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
     "Column 5": "Study name",
-    "Column 6": "Total sample size",
-    "Column 7": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.",
-    "Column 8": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).",
-    "Column 9": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).",
-    "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "OS (Overall Survival)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Treatment regimen",
     "Column 6": "Cancer type",
     "Column 7": "Name of ICI",
     "Column 8": "Control regimen",
     "Column 9": "Monotherapy/combination",
-    "Column 10": "Type of combination"
+    "Column 10": "Trial phase"
   }
 }</t>
   </si>
   <si>
     <t>{
   "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Secondary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Included in MA": "Yes"
+  },
   "selected_column": {
     "Column 1": "NCT",
     "Column 2": "PMID",
@@ -2256,26 +5229,6 @@
     "Column 7": "Name of ICI",
     "Column 8": "Primary endpoint",
     "Column 9": "Total sample size",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "PD-1",
-    "Type of Therapy": "Monotherapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Total sample size",
-    "Column 9": "Trial phase",
     "Column 10": "Clinical setting in relation to surgery"
   }
 }</t>
@@ -2283,67 +5236,8 @@
   <si>
     <t>{
   "selected_filter": {
-    "ICI Class": "PD-L1",
-    "Type of Therapy": "Combination Therapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "CTLA-4",
-    "Type of Therapy": "Monotherapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary Endpoint",
-    "Column 8": "Trial phase",
-    "Column 9": "Total sample size",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "CTLA-4",
-    "Type of Therapy": "Combination Therapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Type of combination",
-    "Column 7": "Name of ICI",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck (HNSCC)",
+    "Trial Phase": "Phase 3",
+    "Cancer Type": "Gastric/GEJ",
     "ICI Class": "PD-L1"
   },
   "selected_column": {
@@ -2352,133 +5246,10 @@
     "Column 3": "Authors",
     "Column 4": "Year",
     "Column 5": "Name of ICI",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Trial phase",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Trial Phase": "Phase 3",
-    "ICI Name": "Pembrolizumab"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Treatment regimen",
-    "Column 7": "Control regimen",
-    "Column 8": "Monotherapy/combination",
-    "Column 9": "Lines of treatment",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Melanoma",
-    "ICI Name": "Nivolumab"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Monotherapy/combination",
-    "Column 6": "Type of combination",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Trial phase",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Breast",
-    "Name of ICI": "Atezolizumab",
-    "Type of Therapy": "Combination Therapy",
-    "Is PD-L1 positivity inclusion criteria": "Yes"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.",
-    "Column 6": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.",
-    "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).",
-    "Column 8": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).",
-    "Column 9": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician's choice).",
-    "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Bladder",
-    "ICI Name": "Avelumab"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Clinical setting in relation to surgery",
-    "Column 6": "Primary Endpoint",
+    "Column 6": "Class of ICI",
     "Column 7": "Treatment regimen",
     "Column 8": "Control regimen",
-    "Column 9": "Monotherapy/combination",
-    "Column 10": "Lines of treatment"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Hepatocellular carcinoma (HCC)",
-    "ICI Name": "Tremelimumab"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Type of combination",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Trial phase",
-    "Column 10": "Monotherapy/combination"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Clinical Setting": "Maintenance"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Trial phase",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
+    "Column 9": "Primary endpoint",
     "Column 10": "Clinical setting in relation to surgery"
   }
 }</t>
@@ -2486,60 +5257,18 @@
   <si>
     <t>{
   "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Trial Phase": "Phase 3",
-    "ICI Class": "PD-1",
-    "Type of Therapy": "Combination Therapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Total sample size",
-    "Column 6": "Primary endpoint",
+    "Cancer Type": "Small Cell Lung Cancer (SCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Secondary endpoint",
     "Column 7": "Name of ICI",
-    "Column 8": "Treatment regimen",
+    "Column 8": "Monotherapy/combination",
     "Column 9": "Control regimen",
-    "Column 10": "Type of combination"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "PD-L1",
-    "Type of Therapy": "Monotherapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary Endpoint",
-    "Column 8": "Total sample size",
-    "Column 9": "Clinical setting in relation to surgery",
-    "Column 10": "Lines of treatment"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination (Treatment Arm)": "ICI + ICI"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary Endpoint",
-    "Column 8": "Total sample size",
-    "Column 9": "Clinical setting in relation to surgery",
     "Column 10": "Trial phase"
   }
 }</t>
@@ -2547,634 +5276,16 @@
   <si>
     <t>{
   "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Type of Therapy": "Combination Therapy",
-    "Type of combination (Treatment Arm)": "ICI + Chemo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Name of ICI",
-    "Column 7": "Control regimen",
-    "Column 8": "Monotherapy/combination",
-    "Column 9": "Lines of treatment",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination (Treatment Arm)": "ICI + RadiatICln (Radiation/Clinical Radiation)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination (Treatment Arm)": "ICI + Vaccine"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Melanoma",
-    "Type of combination (Treatment Arm)": "ICI + BRAFi + MEKi"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Trial phase",
-    "Column 7": "Name of ICI",
-    "Column 8": "Treatment regimen",
-    "Column 9": "Primary endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination (Treatment Arm)": "ICI + Anti-VEGF"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination (Treatment Arm)": "ICI + Chemo + Anti-VEGF"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Treatment regimen",
-    "Column 7": "Name of ICI",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Treatment regimen",
-    "Column 7": "Name of ICI",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial Phase": "Phase 3",
-    "Type of control": "Placebo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.",
-    "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).",
-    "Column 7": "Type of Therapy",
-    "Column 8": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).",
-    "Column 9": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms.",
-    "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Control Arm": "Chemo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Type of combination",
-    "Column 8": "Clinical Setting in relation to surgery",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Hepatocellular carcinoma (HCC)",
-    "Type of Control": "TKI (Tyrosine Kinase Inhibitor)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Treatment regimen",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Control Arm": "Interferon"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Total sample size",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Control Arm": "Best Supportive Care (BSC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of Therapy",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Control Arm": "Chemo / Anti-EGFR"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Treatment regimen",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Control Arm": "Chemo / Anti-VEGF"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Treatment regimen",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Control Arm": "mTOR inhibitor"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Total sample size",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Control Arm": "Multikinase inhibitor"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Treatment regimen",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Control Arm": "Vaccine"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Treatment regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Total sample size",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Control Arm": "Radiation"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Melanoma",
-    "Clinical Setting": "Adjuvant"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Monotherapy/combination",
-    "Column 7": "Primary Endpoint",
-    "Column 8": "Total sample size",
-    "Column 9": "Treatment regimen",
-    "Column 10": "Control regimen"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Clinical Setting in relation to surgery": "Neoadjuvant"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Name of ICI",
-    "Column 7": "Treatment regimen",
-    "Column 8": "Control regimen",
-    "Column 9": "Trial phase",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "Path CR (Pathologic Complete Response; pCR)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.",
-    "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).",
-    "Column 7": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.",
-    "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician's choice).",
-    "Column 9": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).",
-    "Column 10": "Trial phase - The stage or step in the clinical trial process, typically denoted by a Roman numeral (e.g. I, II, III, IV), which defines the scope, objectives, and duration of the trial."
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "ORR (Objective Response Rate)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.",
-    "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).",
-    "Column 7": "Trial phase - The stage or step in the clinical trial process, typically denoted by a Roman numeral (e.g. I, II, III, IV), which defines the scope, objectives, and duration of the trial.",
-    "Column 8": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).",
-    "Column 9": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.",
-    "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "OS (Overall Survival)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Trial phase",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "PFS (Progression-Free Survival)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.",
-    "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).",
-    "Column 7": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.",
-    "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician's choice).",
-    "Column 9": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "RFS (Recurrence-/Relapse-Free Survival)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Clinical setting in relation to surgery",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "EFS (Event-Free Survival) (in combos like Path CR+EFS)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Treatment regimen",
-    "Column 8": "Control regimen",
-    "Column 9": "Trial phase",
-    "Column 10": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "Safety"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.",
-    "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).",
-    "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician's choice).",
-    "Column 9": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).",
-    "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Is PD-L1 positivity inclusion criteria": "Yes"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Class of ICI",
-    "Column 7": "Monotherapy/combination",
-    "Column 8": "Type of combination",
-    "Column 9": "Control regimen",
-    "Column 10": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Colorectal",
-    "Is any other biomarker used for inclusion": "Yes"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Monotherapy/combination",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Pancreatic Cancer",
-    "Is any other biomarker used for inclusion": "Yes"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Is any other biomarker used for inclusion",
-    "Column 10": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Prostate"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Monotherapy/combination",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Is any other biomarker used for inclusion",
-    "Column 10": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Multiple Myeloma"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Study name",
+    "Cancer Type": "Head and Neck (HNSCC)",
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Cancer type",
     "Column 7": "Name of ICI",
     "Column 8": "Monotherapy/combination",
     "Column 9": "Treatment regimen",
@@ -3185,132 +5296,17 @@
   <si>
     <t>{
   "selected_filter": {
-    "Cancer Type": "Mesothelioma"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Treatment regimen",
-    "Column 6": "Name of ICI",
+    "Cancer Type": "Head and Neck (HNSCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
     "Column 7": "Monotherapy/combination",
-    "Column 8": "Type of combination",
-    "Column 9": "Control regimen",
-    "Column 10": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Original/Follow Up": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Trial phase",
-    "Column 7": "Name of ICI",
-    "Column 8": "Monotherapy/combination",
-    "Column 9": "Primary endpoint",
-    "Column 10": "Follow-up duration for primary endpoint(s) in months"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Melanoma",
-    "Type of Study": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Monotherapy/combination",
-    "Column 8": "Primary endpoint",
-    "Column 9": "Follow-up duration for primary endpoint(s) in months",
-    "Column 10": "Type of follow-up given"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial Phase": "Phase 3",
-    "Primary multiple, composite, or co-primary endpoints?": "Co-primary endpoints"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.",
-    "Column 6": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.",
-    "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).",
-    "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician's choice).",
-    "Column 9": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).",
-    "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "OS (Overall Survival)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.",
-    "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).",
-    "Column 7": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.",
-    "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician's choice).",
-    "Column 9": "Follow-up duration for primary endpoint(s) in months – The amount of follow-up available at the time of the primary analysis, reported in months:\n\t[Overall] – Median follow-up across the entire study population.",
-    "Column 10": "Follow-up duration for primary endpoint(s) in months – The amount of follow-up available at the time of the primary analysis, reported in months:\n\t[Rx] – Median follow-up among participants in the treatment/experimental arm."
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "PFS"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Follow-up duration for primary endpoint(s) in months",
-    "Column 7": "Cancer type",
-    "Column 8": "Name of ICI",
-    "Column 9": "Control regimen",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Number of arms",
-    "Column 6": "Cancer type",
-    "Column 7": "Name of ICI",
-    "Column 8": "Type of combination",
+    "Column 8": "Treatment regimen",
     "Column 9": "Control regimen",
     "Column 10": "Primary endpoint"
   }
@@ -3319,9 +5315,7 @@
   <si>
     <t>{
   "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Clinical Setting": "Metastatic / Recurrent (Unresectable)",
-    "Lines of treatment": "1L"
+    "Cancer Type": "Renal Cell Carcinoma (RCC)"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -3330,49 +5324,29 @@
     "Column 4": "Year",
     "Column 5": "Name of ICI",
     "Column 6": "Class of ICI",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Bladder",
-    "Lines of treatment": "2L"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Monotherapy/combination",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Total sample size",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck (HNSCC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
+    "Column 7": "Lines of treatment",
+    "Column 8": "Clinical setting in relation to surgery",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Clinical Setting": "Perioperative"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
     "Column 6": "Name of ICI",
     "Column 7": "Monotherapy/combination",
     "Column 8": "Treatment regimen",
     "Column 9": "Control regimen",
-    "Column 10": "Trial phase"
+    "Column 10": "Primary endpoint"
   }
 }</t>
   </si>
@@ -3380,955 +5354,7 @@
     <t>{
   "selected_filter": {
     "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Trial Phase": "Phase 3"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Name of ICI",
-    "Column 8": "Control regimen",
-    "Column 9": "Monotherapy/combination",
-    "Column 10": "Lines of treatment"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Melanoma",
-    "Type of Therapy": "Combination Therapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Secondary endpoint",
-    "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.",
-    "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).",
-    "Column 8": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.",
-    "Column 9": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician's choice).",
-    "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of Study": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Type of follow-up given",
-    "Column 6": "Follow-up duration for primary endpoint(s) in months",
-    "Column 7": "Primary Endpoint",
-    "Column 8": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.",
-    "Column 9": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).",
-    "Column 10": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details."
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Included in MA": "Yes"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Included in MA": "No"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Renal Cell Carcinoma (RCC)",
-    "Type of Study": "Original publication"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Monotherapy/combination",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Total sample size",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Gastric/GEJ",
-    "Trial Phase": "Phase 3",
-    "ICI Class": "PD-L1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Treatment regimen",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Total sample size",
-    "Column 10": "Monotherapy/combination"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Esophageal/GEJ",
-    "ICI Class": "PD-1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Name of ICI",
-    "Column 7": "Monotherapy/combination",
-    "Column 8": "Type of combination",
-    "Column 9": "Control regimen",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Small Cell Lung Cancer (SCLC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Name of ICI",
-    "Column 7": "Monotherapy/combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Trial phase",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck (HNSCC)",
-    "Primary Endpoint": "OS (Overall Survival)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Trial phase",
-    "Column 7": "Treatment regimen",
-    "Column 8": "Control regimen",
-    "Column 9": "Name of ICI",
-    "Column 10": "Monotherapy/combination"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck (HNSCC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Breast"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Class of ICI",
-    "Column 7": "Monotherapy/combination",
-    "Column 8": "Type of combination",
-    "Column 9": "Control regimen",
-    "Column 10": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Gastric/GEJ",
-    "Lines of treatment": "2L"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of Therapy",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Hepatocellular carcinoma (HCC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Treatment regimen",
-    "Column 7": "Control regimen",
-    "Column 8": "Lines of treatment",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Monotherapy/combination"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Renal Cell Carcinoma (RCC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Lines of treatment",
-    "Column 6": "Name of ICI",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Monotherapy/combination",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Clinical setting in relation to surgery": "Perioperative"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Treatment regimen",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Clinical Setting": "Metastatic / Recurrent (Unresectable)",
-    "Lines of treatment": "2L"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Class of ICI",
-    "Column 7": "Monotherapy/combination",
-    "Column 8": "Type of combination",
-    "Column 9": "Control regimen",
-    "Column 10": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Class of ICI",
-    "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.",
-    "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).",
-    "Column 8": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.",
-    "Column 9": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician's choice).",
-    "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination (Treatment Arm)": "ICI + MEKi"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of combination",
-    "Column 8": "Primary endpoint",
-    "Column 9": "Total sample size",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "ICI Class": "PD-1",
-    "Trial Phase": "Phase 3"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Class of ICI",
-    "Column 7": "Monotherapy/combination",
-    "Column 8": "Type of combination",
-    "Column 9": "Control regimen",
-    "Column 10": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Melanoma"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Monotherapy/combination",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck (HNSCC)",
-    "Type of Therapy": "Combination Therapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Type of combination",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Total sample size",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Is PD-L1 positivity inclusion criteria": "No"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Class of ICI",
-    "Column 7": "Monotherapy/combination",
-    "Column 8": "Type of combination",
-    "Column 9": "Control regimen",
-    "Column 10": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial Phase": "Phase 3"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Monotherapy/combination",
-    "Column 8": "Primary endpoint",
-    "Column 9": "Total sample size",
-    "Column 10": "Control regimen"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Renal Cell Carcinoma (RCC)",
-    "Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)",
-    "Type of Therapy": "Combination Therapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Type of combination",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Trial phase",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Small Cell Lung Cancer (SCLC)",
-    "Type of Therapy": "Combination Therapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Treatment regimen",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Trial phase",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant",
-    "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab)",
-    "Column 7": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination)",
-    "Column 8": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)",
-    "Column 9": "Trial phase",
-    "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Type of combination (Treatment Arm)": "ICI + ICI"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Type of combination",
-    "Column 7": "Primary Endpoint",
-    "Column 8": "Clinical Setting in relation to surgery",
-    "Column 9": "Trial phase",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Lines of treatment": "2L+"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Follow-up duration for primary endpoint(s) in months",
-    "Column 6": "Cancer type",
-    "Column 7": "Name of ICI",
-    "Column 8": "Treatment regimen",
-    "Column 9": "Control regimen",
-    "Column 10": "Primary endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Melanoma",
-    "Clinical Setting": "Adjuvant",
-    "ICI Name": "Pembrolizumab"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary Endpoint",
-    "Column 7": "Total sample size",
-    "Column 8": "Treatment regimen",
-    "Column 9": "Control regimen",
-    "Column 10": "Monotherapy/combination"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Bladder",
-    "Trial Phase": "Phase 3",
-    "Type of Therapy": "Monotherapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Primary Endpoint",
-    "Column 7": "Control regimen",
-    "Column 8": "Follow-up duration for primary endpoint(s) in months",
-    "Column 9": "Total sample size",
-    "Column 10": "Lines of treatment"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "PD-L1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Monotherapy/combination",
-    "Column 8": "Type of combination",
-    "Column 9": "Control regimen",
-    "Column 10": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Total sample size",
-    "Column 7": "Cancer type",
-    "Column 8": "Name of ICI",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "OS (Overall Survival)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.",
-    "Column 6": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.",
-    "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).",
-    "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician's choice).",
-    "Column 9": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).",
-    "Column 10": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos."
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Cancer type",
-    "Column 7": "Name of ICI",
-    "Column 8": "Trial phase",
-    "Column 9": "Primary endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "CTLA-4",
-    "Type of Therapy": "Monotherapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary Endpoint",
-    "Column 8": "Total sample size",
-    "Column 9": "Clinical setting in relation to surgery",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Breast",
-    "Name of ICI": "Atezolizumab",
-    "Type of Therapy": "Combination Therapy",
-    "Is PD-L1 positivity inclusion criteria": "Yes"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary Endpoint",
-    "Column 7": "Treatment regimen",
-    "Column 8": "Control regimen",
-    "Column 9": "Monotherapy/combination",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Hepatocellular carcinoma (HCC)",
-    "ICI Name": "Tremelimumab"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Type of combination",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Trial phase",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination (Treatment Arm)": "ICI + Vaccine"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Melanoma",
-    "Type of combination (Treatment Arm)": "ICI + BRAFi + MEKi"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Trial phase",
-    "Column 7": "Name of ICI",
-    "Column 8": "Treatment regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Control Arm": "mTOR inhibitor"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Total sample size",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Control Arm": "Vaccine"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Treatment regimen",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Control Arm": "Radiation"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Treatment regimen",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Clinical Setting in relation to surgery": "Neoadjuvant"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Name of ICI",
-    "Column 8": "Treatment regimen",
-    "Column 9": "Control regimen",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "OS (Overall Survival)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Cancer type",
-    "Column 7": "Name of ICI",
-    "Column 8": "Control regimen",
-    "Column 9": "Monotherapy/combination",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "PFS (Progression-Free Survival)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Monotherapy/combination",
-    "Column 8": "Type of combination",
-    "Column 9": "Control regimen",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "Safety"
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -4339,7 +5365,7 @@
     "Column 6": "Name of ICI",
     "Column 7": "Monotherapy/combination",
     "Column 8": "Control regimen",
-    "Column 9": "Trial phase",
+    "Column 9": "Lines of treatment",
     "Column 10": "Primary endpoint"
   }
 }</t>
@@ -4347,67 +5373,7 @@
   <si>
     <t>{
   "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Type of Study": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Trial phase",
-    "Column 7": "Name of ICI",
-    "Column 8": "Primary endpoint",
-    "Column 9": "Follow-up duration for primary endpoint(s) in months",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial Phase": "Phase 2"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Number of arms",
-    "Column 6": "Cancer type",
-    "Column 7": "Name of ICI",
-    "Column 8": "Type of combination",
-    "Column 9": "Control regimen",
-    "Column 10": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Clinical Setting": "Metastatic / Recurrent (Unresectable)",
-    "Lines of treatment": "Lines of treatment"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Melanoma"
+    "Type of combination (Treatment Arm)": "ICI + MEKi"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -4417,59 +5383,8 @@
     "Column 5": "Study name",
     "Column 6": "Name of ICI",
     "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Type of follow-up given"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Included in MA": "No"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Trial phase",
-    "Column 9": "Type of combination",
-    "Column 10": "Control regimen"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Esophageal/GEJ",
-    "ICI Class": "PD-1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Name of ICI",
-    "Column 7": "Monotherapy/combination",
-    "Column 8": "Treatment regimen",
-    "Column 9": "Control regimen",
+    "Column 8": "Cancer type",
+    "Column 9": "Treatment regimen",
     "Column 10": "Trial phase"
   }
 }</t>
@@ -4477,383 +5392,14 @@
   <si>
     <t>{
   "selected_filter": {
-    "Cancer Type": "Small Cell Lung Cancer (SCLC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Name of ICI",
-    "Column 7": "Monotherapy/combination",
-    "Column 8": "Treatment regimen",
-    "Column 9": "Control regimen",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck (HNSCC)",
-    "Primary Endpoint": "OS (Overall Survival)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Trial phase",
-    "Column 7": "Name of ICI",
-    "Column 8": "Monotherapy/combination",
-    "Column 9": "Type of combination",
-    "Column 10": "Control regimen"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck (HNSCC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Primary Endpoint",
-    "Column 8": "Control regimen",
-    "Column 9": "Trial phase",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Breast"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Gastric/GEJ",
-    "Lines of treatment": "2L"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Treatment regimen",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
   "selected_column": {
     "Column 1": "NCT",
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
     "Column 5": "Class of ICI",
-    "Column 6": "Cancer type",
-    "Column 7": "Name of ICI",
-    "Column 8": "Trial phase",
-    "Column 9": "Primary endpoint",
-    "Column 10": "Type of combination"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Melanoma"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Monotherapy/combination",
-    "Column 7": "Primary Endpoint",
-    "Column 8": "Treatment regimen",
-    "Column 9": "Control regimen",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Is PD-L1 positivity inclusion criteria": "No"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Trial phase",
-    "Column 10": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial Phase": "Phase 3"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of Therapy",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Control regimen",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Treatment regimen",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Type of combination (Treatment Arm)": "ICI + ICI"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Type of combination",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Trial phase",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Follow-up duration for primary endpoint(s) in months",
-    "Column 6": "Cancer type",
-    "Column 7": "Name of ICI",
-    "Column 8": "Treatment regimen",
-    "Column 9": "Control regimen",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "PD-1",
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Treatment regimen",
-    "Column 6": "Name of ICI",
-    "Column 7": "Monotherapy/combination",
-    "Column 8": "Type of combination",
-    "Column 9": "Control regimen",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "CTLA-4",
-    "Type of Therapy": "Combination Therapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.",
-    "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).",
-    "Column 7": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.",
-    "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician's choice).",
-    "Column 9": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).",
-    "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Trial Phase": "Phase 3",
-    "ICI Class": "PD-1",
-    "Type of Therapy": "Combination Therapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Total sample size",
-    "Column 7": "Name of ICI",
-    "Column 8": "Control regimen",
-    "Column 9": "Monotherapy/combination",
-    "Column 10": "Lines of treatment"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Treatment regimen",
-    "Column 7": "Name of ICI",
-    "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial Phase": "Phase 3",
-    "Type of Control": "Placebo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Total sample size",
-    "Column 9": "Monotherapy/combination",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Control Arm": "Chemo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Trial phase",
-    "Column 7": "Name of ICI",
-    "Column 8": "Type of combination",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "RFS (Recurrence-/Relapse-Free Survival)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
-    "Column 6": "Name of ICI",
-    "Column 7": "Type of combination",
-    "Column 8": "Control regimen",
-    "Column 9": "Clinical setting in relation to surgery",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "EFS (Event-Free Survival) (in combos like Path CR+EFS)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer type",
     "Column 6": "Name of ICI",
     "Column 7": "Type of combination",
     "Column 8": "Control regimen",
@@ -4865,8 +5411,8 @@
   <si>
     <t>{
   "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Is PD-L1 positivity inclusion criteria": "Yes"
+    "Cancer Type": "Head and Neck (HNSCC)",
+    "Type of Therapy": "Combination Therapy"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -4874,145 +5420,53 @@
     "Column 3": "Authors",
     "Column 4": "Year",
     "Column 5": "Name of ICI",
-    "Column 6": "Monotherapy/combination",
+    "Column 6": "Class of ICI",
     "Column 7": "Type of combination",
     "Column 8": "Control regimen",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Pancreatic Cancer",
-    "Is any other biomarker used for inclusion": "Yes"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Monotherapy/combination",
-    "Column 7": "Type of combination",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of Therapy": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Name of ICI",
+    "Column 8": "Type of combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of Therapy": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
     "Column 8": "Control regimen",
-    "Column 9": "Is any other biomarker used for inclusion",
-    "Column 10": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Multiple Myeloma"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Name of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "PFS"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Follow-up duration for primary endpoint(s) in months",
-    "Column 7": "Cancer type",
-    "Column 8": "Name of ICI",
-    "Column 9": "Treatment regimen",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Renal Cell Carcinoma (RCC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Monotherapy/combination",
-    "Column 7": "Lines of treatment",
-    "Column 8": "Clinical setting in relation to surgery",
-    "Column 9": "Primary Endpoint",
-    "Column 10": "Control regimen"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Lines of treatment": "2L"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Monotherapy/combination",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Total sample size",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck (HNSCC)",
-    "Type of Therapy": "Combination Therapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Type of combination",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint",
-    "Column 9": "Trial phase",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Melanoma",
-    "Clinical Setting": "Adjuvant",
-    "ICI Name": "Pembrolizumab"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary Endpoint",
-    "Column 7": "Total sample size",
-    "Column 8": "Treatment regimen",
-    "Column 9": "Control regimen",
-    "Column 10": "Trial phase"
+    "Column 9": "Primary endpoint",
+    "Column 10": "Clinical setting in relation to surgery"
   }
 }</t>
   </si>
@@ -5406,7 +5860,7 @@
         <v>205</v>
       </c>
       <c r="E2" t="s">
-        <v>341</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5420,7 +5874,7 @@
         <v>206</v>
       </c>
       <c r="D3" t="s">
-        <v>206</v>
+        <v>305</v>
       </c>
       <c r="E3" t="s">
         <v>206</v>
@@ -5440,7 +5894,7 @@
         <v>207</v>
       </c>
       <c r="E4" t="s">
-        <v>207</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5454,10 +5908,10 @@
         <v>208</v>
       </c>
       <c r="D5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5471,7 +5925,7 @@
         <v>209</v>
       </c>
       <c r="D6" t="s">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="E6" t="s">
         <v>209</v>
@@ -5505,7 +5959,7 @@
         <v>211</v>
       </c>
       <c r="D8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E8" t="s">
         <v>211</v>
@@ -5522,7 +5976,7 @@
         <v>212</v>
       </c>
       <c r="D9" t="s">
-        <v>307</v>
+        <v>212</v>
       </c>
       <c r="E9" t="s">
         <v>212</v>
@@ -5539,10 +5993,10 @@
         <v>213</v>
       </c>
       <c r="D10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5556,10 +6010,10 @@
         <v>214</v>
       </c>
       <c r="D11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E11" t="s">
-        <v>309</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5573,7 +6027,7 @@
         <v>215</v>
       </c>
       <c r="D12" t="s">
-        <v>215</v>
+        <v>311</v>
       </c>
       <c r="E12" t="s">
         <v>215</v>
@@ -5593,7 +6047,7 @@
         <v>216</v>
       </c>
       <c r="E13" t="s">
-        <v>216</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5607,10 +6061,10 @@
         <v>217</v>
       </c>
       <c r="D14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E14" t="s">
-        <v>310</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5624,10 +6078,10 @@
         <v>218</v>
       </c>
       <c r="D15" t="s">
-        <v>218</v>
+        <v>313</v>
       </c>
       <c r="E15" t="s">
-        <v>342</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5644,7 +6098,7 @@
         <v>219</v>
       </c>
       <c r="E16" t="s">
-        <v>219</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -5658,7 +6112,7 @@
         <v>220</v>
       </c>
       <c r="D17" t="s">
-        <v>220</v>
+        <v>314</v>
       </c>
       <c r="E17" t="s">
         <v>220</v>
@@ -5692,10 +6146,10 @@
         <v>222</v>
       </c>
       <c r="D19" t="s">
-        <v>311</v>
+        <v>222</v>
       </c>
       <c r="E19" t="s">
-        <v>222</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -5709,7 +6163,7 @@
         <v>223</v>
       </c>
       <c r="D20" t="s">
-        <v>223</v>
+        <v>315</v>
       </c>
       <c r="E20" t="s">
         <v>223</v>
@@ -5726,7 +6180,7 @@
         <v>224</v>
       </c>
       <c r="D21" t="s">
-        <v>312</v>
+        <v>224</v>
       </c>
       <c r="E21" t="s">
         <v>224</v>
@@ -5763,7 +6217,7 @@
         <v>226</v>
       </c>
       <c r="E23" t="s">
-        <v>343</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -5777,10 +6231,10 @@
         <v>227</v>
       </c>
       <c r="D24" t="s">
-        <v>227</v>
+        <v>316</v>
       </c>
       <c r="E24" t="s">
-        <v>227</v>
+        <v>316</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -5794,7 +6248,7 @@
         <v>228</v>
       </c>
       <c r="D25" t="s">
-        <v>228</v>
+        <v>317</v>
       </c>
       <c r="E25" t="s">
         <v>228</v>
@@ -5814,7 +6268,7 @@
         <v>229</v>
       </c>
       <c r="E26" t="s">
-        <v>229</v>
+        <v>353</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -5831,7 +6285,7 @@
         <v>230</v>
       </c>
       <c r="E27" t="s">
-        <v>230</v>
+        <v>354</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -5862,7 +6316,7 @@
         <v>232</v>
       </c>
       <c r="D29" t="s">
-        <v>313</v>
+        <v>232</v>
       </c>
       <c r="E29" t="s">
         <v>232</v>
@@ -5879,10 +6333,10 @@
         <v>233</v>
       </c>
       <c r="D30" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E30" t="s">
-        <v>314</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -5896,7 +6350,7 @@
         <v>234</v>
       </c>
       <c r="D31" t="s">
-        <v>234</v>
+        <v>319</v>
       </c>
       <c r="E31" t="s">
         <v>234</v>
@@ -5913,10 +6367,10 @@
         <v>235</v>
       </c>
       <c r="D32" t="s">
-        <v>235</v>
+        <v>320</v>
       </c>
       <c r="E32" t="s">
-        <v>235</v>
+        <v>320</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -5930,10 +6384,10 @@
         <v>236</v>
       </c>
       <c r="D33" t="s">
+        <v>321</v>
+      </c>
+      <c r="E33" t="s">
         <v>236</v>
-      </c>
-      <c r="E33" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -5947,10 +6401,10 @@
         <v>237</v>
       </c>
       <c r="D34" t="s">
+        <v>322</v>
+      </c>
+      <c r="E34" t="s">
         <v>237</v>
-      </c>
-      <c r="E34" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -5964,10 +6418,10 @@
         <v>238</v>
       </c>
       <c r="D35" t="s">
+        <v>323</v>
+      </c>
+      <c r="E35" t="s">
         <v>238</v>
-      </c>
-      <c r="E35" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -5984,7 +6438,7 @@
         <v>239</v>
       </c>
       <c r="E36" t="s">
-        <v>239</v>
+        <v>355</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6018,7 +6472,7 @@
         <v>241</v>
       </c>
       <c r="E38" t="s">
-        <v>241</v>
+        <v>356</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6032,7 +6486,7 @@
         <v>242</v>
       </c>
       <c r="D39" t="s">
-        <v>242</v>
+        <v>324</v>
       </c>
       <c r="E39" t="s">
         <v>242</v>
@@ -6049,10 +6503,10 @@
         <v>243</v>
       </c>
       <c r="D40" t="s">
-        <v>243</v>
+        <v>325</v>
       </c>
       <c r="E40" t="s">
-        <v>243</v>
+        <v>325</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6066,10 +6520,10 @@
         <v>244</v>
       </c>
       <c r="D41" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="E41" t="s">
-        <v>315</v>
+        <v>244</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -6100,10 +6554,10 @@
         <v>246</v>
       </c>
       <c r="D43" t="s">
-        <v>316</v>
+        <v>246</v>
       </c>
       <c r="E43" t="s">
-        <v>316</v>
+        <v>246</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -6117,7 +6571,7 @@
         <v>247</v>
       </c>
       <c r="D44" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="E44" t="s">
         <v>247</v>
@@ -6151,10 +6605,10 @@
         <v>249</v>
       </c>
       <c r="D46" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="E46" t="s">
-        <v>249</v>
+        <v>328</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -6171,7 +6625,7 @@
         <v>250</v>
       </c>
       <c r="E47" t="s">
-        <v>250</v>
+        <v>357</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6202,10 +6656,10 @@
         <v>252</v>
       </c>
       <c r="D49" t="s">
-        <v>319</v>
+        <v>252</v>
       </c>
       <c r="E49" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -6219,7 +6673,7 @@
         <v>253</v>
       </c>
       <c r="D50" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E50" t="s">
         <v>253</v>
@@ -6236,10 +6690,10 @@
         <v>254</v>
       </c>
       <c r="D51" t="s">
-        <v>254</v>
+        <v>330</v>
       </c>
       <c r="E51" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -6253,10 +6707,10 @@
         <v>255</v>
       </c>
       <c r="D52" t="s">
-        <v>255</v>
+        <v>331</v>
       </c>
       <c r="E52" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -6270,10 +6724,10 @@
         <v>256</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>256</v>
       </c>
       <c r="E53" t="s">
-        <v>256</v>
+        <v>359</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -6287,10 +6741,10 @@
         <v>257</v>
       </c>
       <c r="D54" t="s">
+        <v>332</v>
+      </c>
+      <c r="E54" t="s">
         <v>257</v>
-      </c>
-      <c r="E54" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -6304,7 +6758,7 @@
         <v>258</v>
       </c>
       <c r="D55" t="s">
-        <v>258</v>
+        <v>333</v>
       </c>
       <c r="E55" t="s">
         <v>258</v>
@@ -6324,7 +6778,7 @@
         <v>259</v>
       </c>
       <c r="E56" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -6338,10 +6792,10 @@
         <v>260</v>
       </c>
       <c r="D57" t="s">
-        <v>260</v>
+        <v>334</v>
       </c>
       <c r="E57" t="s">
-        <v>260</v>
+        <v>334</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -6355,10 +6809,10 @@
         <v>261</v>
       </c>
       <c r="D58" t="s">
-        <v>261</v>
+        <v>335</v>
       </c>
       <c r="E58" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -6375,7 +6829,7 @@
         <v>262</v>
       </c>
       <c r="E59" t="s">
-        <v>262</v>
+        <v>361</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -6389,7 +6843,7 @@
         <v>263</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>263</v>
       </c>
       <c r="E60" t="s">
         <v>263</v>
@@ -6409,7 +6863,7 @@
         <v>264</v>
       </c>
       <c r="E61" t="s">
-        <v>264</v>
+        <v>362</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -6460,7 +6914,7 @@
         <v>267</v>
       </c>
       <c r="E64" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -6474,10 +6928,10 @@
         <v>268</v>
       </c>
       <c r="D65" t="s">
-        <v>323</v>
+        <v>268</v>
       </c>
       <c r="E65" t="s">
-        <v>323</v>
+        <v>268</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -6491,10 +6945,10 @@
         <v>269</v>
       </c>
       <c r="D66" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="E66" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -6508,10 +6962,10 @@
         <v>270</v>
       </c>
       <c r="D67" t="s">
-        <v>270</v>
+        <v>337</v>
       </c>
       <c r="E67" t="s">
-        <v>270</v>
+        <v>337</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -6525,7 +6979,7 @@
         <v>271</v>
       </c>
       <c r="D68" t="s">
-        <v>271</v>
+        <v>338</v>
       </c>
       <c r="E68" t="s">
         <v>271</v>
@@ -6545,7 +6999,7 @@
         <v>272</v>
       </c>
       <c r="E69" t="s">
-        <v>272</v>
+        <v>364</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -6559,10 +7013,10 @@
         <v>273</v>
       </c>
       <c r="D70" t="s">
-        <v>325</v>
+        <v>273</v>
       </c>
       <c r="E70" t="s">
-        <v>325</v>
+        <v>273</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -6579,7 +7033,7 @@
         <v>274</v>
       </c>
       <c r="E71" t="s">
-        <v>274</v>
+        <v>365</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -6593,7 +7047,7 @@
         <v>275</v>
       </c>
       <c r="D72" t="s">
-        <v>326</v>
+        <v>275</v>
       </c>
       <c r="E72" t="s">
         <v>275</v>
@@ -6613,7 +7067,7 @@
         <v>276</v>
       </c>
       <c r="E73" t="s">
-        <v>276</v>
+        <v>366</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -6627,10 +7081,10 @@
         <v>277</v>
       </c>
       <c r="D74" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="E74" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -6644,10 +7098,10 @@
         <v>278</v>
       </c>
       <c r="D75" t="s">
-        <v>278</v>
+        <v>339</v>
       </c>
       <c r="E75" t="s">
-        <v>278</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -6664,7 +7118,7 @@
         <v>279</v>
       </c>
       <c r="E76" t="s">
-        <v>279</v>
+        <v>367</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -6678,10 +7132,10 @@
         <v>280</v>
       </c>
       <c r="D77" t="s">
-        <v>328</v>
+        <v>280</v>
       </c>
       <c r="E77" t="s">
-        <v>328</v>
+        <v>280</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -6695,10 +7149,10 @@
         <v>281</v>
       </c>
       <c r="D78" t="s">
-        <v>329</v>
+        <v>281</v>
       </c>
       <c r="E78" t="s">
-        <v>329</v>
+        <v>368</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -6712,10 +7166,10 @@
         <v>282</v>
       </c>
       <c r="D79" t="s">
-        <v>330</v>
+        <v>282</v>
       </c>
       <c r="E79" t="s">
-        <v>330</v>
+        <v>369</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -6729,10 +7183,10 @@
         <v>283</v>
       </c>
       <c r="D80" t="s">
-        <v>331</v>
+        <v>283</v>
       </c>
       <c r="E80" t="s">
-        <v>283</v>
+        <v>370</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -6746,7 +7200,7 @@
         <v>284</v>
       </c>
       <c r="D81" t="s">
-        <v>332</v>
+        <v>284</v>
       </c>
       <c r="E81" t="s">
         <v>284</v>
@@ -6763,10 +7217,10 @@
         <v>285</v>
       </c>
       <c r="D82" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="E82" t="s">
-        <v>285</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -6800,7 +7254,7 @@
         <v>287</v>
       </c>
       <c r="E84" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -6817,7 +7271,7 @@
         <v>288</v>
       </c>
       <c r="E85" t="s">
-        <v>288</v>
+        <v>372</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -6834,7 +7288,7 @@
         <v>289</v>
       </c>
       <c r="E86" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -6848,7 +7302,7 @@
         <v>290</v>
       </c>
       <c r="D87" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
       <c r="E87" t="s">
         <v>290</v>
@@ -6868,7 +7322,7 @@
         <v>291</v>
       </c>
       <c r="E88" t="s">
-        <v>291</v>
+        <v>374</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -6885,7 +7339,7 @@
         <v>292</v>
       </c>
       <c r="E89" t="s">
-        <v>292</v>
+        <v>375</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -6899,10 +7353,10 @@
         <v>293</v>
       </c>
       <c r="D90" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E90" t="s">
-        <v>335</v>
+        <v>293</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -6919,7 +7373,7 @@
         <v>294</v>
       </c>
       <c r="E91" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -6933,7 +7387,7 @@
         <v>295</v>
       </c>
       <c r="D92" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="E92" t="s">
         <v>295</v>
@@ -6950,10 +7404,10 @@
         <v>296</v>
       </c>
       <c r="D93" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E93" t="s">
-        <v>337</v>
+        <v>296</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -6967,10 +7421,10 @@
         <v>297</v>
       </c>
       <c r="D94" t="s">
-        <v>297</v>
+        <v>344</v>
       </c>
       <c r="E94" t="s">
-        <v>297</v>
+        <v>344</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -6984,10 +7438,10 @@
         <v>298</v>
       </c>
       <c r="D95" t="s">
-        <v>298</v>
+        <v>345</v>
       </c>
       <c r="E95" t="s">
-        <v>298</v>
+        <v>345</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -7001,10 +7455,10 @@
         <v>299</v>
       </c>
       <c r="D96" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="E96" t="s">
-        <v>299</v>
+        <v>377</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -7035,10 +7489,10 @@
         <v>301</v>
       </c>
       <c r="D98" t="s">
-        <v>339</v>
+        <v>301</v>
       </c>
       <c r="E98" t="s">
-        <v>339</v>
+        <v>378</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -7052,7 +7506,7 @@
         <v>302</v>
       </c>
       <c r="D99" t="s">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="E99" t="s">
         <v>302</v>
@@ -7069,10 +7523,10 @@
         <v>303</v>
       </c>
       <c r="D100" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E100" t="s">
-        <v>303</v>
+        <v>347</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -7086,10 +7540,10 @@
         <v>304</v>
       </c>
       <c r="D101" t="s">
+        <v>348</v>
+      </c>
+      <c r="E101" t="s">
         <v>304</v>
-      </c>
-      <c r="E101" t="s">
-        <v>356</v>
       </c>
     </row>
   </sheetData>
